--- a/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
+++ b/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:31:55+00:00</t>
+    <t>2026-06-12T13:24:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
+++ b/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T13:24:30+00:00</t>
+    <t>2026-06-12T14:36:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
+++ b/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:36:22+00:00</t>
+    <t>2026-06-12T14:51:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
+++ b/feature/new-ig-template/ig/StructureDefinition-FrLocationAgregateur.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:51:06+00:00</t>
+    <t>2026-06-15T12:26:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
